--- a/backend/VIT_EventHub_Filled.xlsx
+++ b/backend/VIT_EventHub_Filled.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All 200+ Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1865,31 +1865,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mr.Physique</t>
+          <t>Three to Tango | Sketch Guess Design</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Three to Tango | Sketch Guess Design</t>
+          <t>Voices for Tomorrow</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1898,18 +1898,18 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Voices for Tomorrow</t>
+          <t>Haryana Hood Mela</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1925,31 +1925,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Haryana Hood Mela</t>
+          <t>The Last Clue Bleeds</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>The Last Clue Bleeds</t>
+          <t>Campus Quest</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Campus Quest</t>
+          <t>Lights, Camera, Walk</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lights, Camera, Walk</t>
+          <t>Flowspace</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2005,40 +2005,2900 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Flowspace</t>
+          <t>Magadh Mahotsav</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Magadh Mahotsav</t>
+          <t>The Yokai's Residence</t>
         </is>
       </c>
       <c r="B81" t="n">
+        <v>200</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>VITopoly Rush 2.0</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>100</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20-Second Reel Challenge</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
         <v>50</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Song Association</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>50</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Campus undercover</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>100</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Movie surfing</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>100</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Task master</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>100</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Emergency Exit 3.0</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>50</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>The Yokai's Residence</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>140</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Campus Conspiracy</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>179</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Midnight Protocol</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>50</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PLAYVERSE: The Ultimate Campus Game Arena</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>50</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Case closed - Uncover the truth</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>70</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Riverdale Reckonings</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>150</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DECODEX: The Mystery Hunt</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>150</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Quizzipedia - the internet quiz</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>100</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Laser tag</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>300</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-02-18 To 2026-02-21</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Grand Prix de la francophonie</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>100</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>RenderX</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>100</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>The Case Files A Murder Mystery Challenge</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>60</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>The Crowd Says</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>120</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Minecraft Showdown</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>150</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Fact Check</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>50</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>The Hotseat (KBC)</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>100</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IPL Auction Battle 6.0</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>150</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Monopoly Stock Market</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>50</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Global Idea Roulette</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>50</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Eco Shark Tank</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>120</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Beaded Bonds</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>75</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Litsoc Arcade-Insert Coin Here</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>50</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Photon Escape</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>50</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Escape Room: Engineers Gambit</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>150</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sye</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>50</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Global Idea Roulette</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>75</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Global Idea Roulette</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>100</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Olympics '26</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>100</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Anime Auction: Battle of Builds</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>100</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>THE CROWD SAYS</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>150</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Everything, Everywhere, All at once</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>100</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Fact Check</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>100</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Eco Shark Tank</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>150</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Three to Tango | Sketch • Guess • Design</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>150</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Valoverse</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>300</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VOICES OF IMPACT</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>75</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CLICK-N-SHIFT ADVENTURE</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>140</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VOICES OF IMPACT</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PUNJAB'S ENIGMA</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>100</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PUNJAB'S ENIGMA</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>180</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HOUSIE HUNGAMA</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>80</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HOUSIE HUNGAMA</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>140</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VOICES OF IMPACT</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>100</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CLICK-N-SHIFT ADVENTURE</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>175</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Death Mania</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>300</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>The Case Files A Murder Mystery Challenge</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>100</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Quizzipedia - the internet quiz</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>200</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Namma Mela 2.0 - Arm Wrestling</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>50</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Escape the Boardroom</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>90</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Escape the Boardroom</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>110</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IPL Auction Battle 6.0</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>250</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IPL Auction Battle 6.0</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>300</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Therottam</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>100</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dev Dine 2.0</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>500</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Art carnival - Pair painting</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>50</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Haryana Hood Mela</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>320</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CODE RED</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>150</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CODE RED</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>150</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Operation Wellcode</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>80</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Ground Zero</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>150</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Dare Dashers 3.0</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>75</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Campus Quest</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>100</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Anime Auction: Battle of Builds</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>80</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Aurora 2.0</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>250</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DudePerfect Basketball Edition</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>50</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Kill Socrates: The Socratic Courtroom</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>130</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Emergency Exit 3.0</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>75</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Campus Quest</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>120</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Arcade Arena</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>100</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DudePerfect Football Edition</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>50</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Valoverse</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>60</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Campus undercover</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>275</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Kill Socrates: The Socratic Courtroom</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>80</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DESI ARCADE</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>50</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Case closed - Uncover the truth</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>100</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>The Great Prompt Off</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>150</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Rhythmic reflections 2.1</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>70</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Mission Apollo: The Last Exit</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>100</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Case closed - Uncover the truth</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>90</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Polaroid Photobooth</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>278</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>The Secret Agenda</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>150</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Shipwreck: The Last Survivor</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>130</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Mission Apollo: The Last Exit</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>150</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Quizzipedia - the internet quiz</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>150</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Everything, Everywhere, All at once</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>150</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Everything, Everywhere, All at once</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>200</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>DESI ARCADE</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>70</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Clicks and Clay</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>180</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Song Association</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>60</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>The Last Clue Bleeds</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>90</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>The Last Clue Bleeds</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>100</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Clicks and Clay</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>150</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Clicks and Clay</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>120</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DANCEPACITO</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>10 - 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DESI ARCADE</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>100</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>IPL AUCTION</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>150</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DESI ARCADE</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>90</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Art carnival - Caricature</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>100</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>IPL AUCTION</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>120</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DECODEX: The Mystery Hunt</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>200</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Escape the Haunted House</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>180</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-02-18 To 2026-02-21</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>The Case Files A Murder Mystery Challenge</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>80</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Escape the Haunted House</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>150</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-02-18 To 2026-02-21</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Escape the Boardroom</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>75</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PROMPTWOOD PICTURES</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>100</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Chameleon</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>250</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Death Mania</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>150</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Polyphony - Western Battle of Bands</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>300</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Death Mania</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>50</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SPAR: The floor is yours</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>450</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Component Chaos</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>150</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Component Chaos</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>100</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Gameshift</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>150</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>GAMESHIFT</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>250</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Ground Zero</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>50</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GAMESHIFT</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>200</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hostel Accommodation</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>400</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-02-18 To 2026-02-22</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>debate ae democracy</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>80</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Aakriti - Eastern Battle of Bands</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>300</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Namma Mela 2.0 - Canvas Painting</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>75</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>UNLOCK-AI</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>50</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Monopoly Stock Market</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>100</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Shipwreck: The Last Survivor</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>80</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DANCING DRAMA</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>500</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>IPL AUCTION</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>140</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Task master</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>150</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Aaravam</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>100</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Tentkotta</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>100</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>25</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>50</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>75</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>100</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>150</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>UTSAV 4.0</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>200</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Rhythms Of Odisha</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>50</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SherlockIT! 2.0: Multiverse Edition</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>50</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
